--- a/public/files/templates/Template_Dosen.xlsx
+++ b/public/files/templates/Template_Dosen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP Victus\Desktop\Asesmen-CPL\public\files\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAA9B58-6061-46B8-B30F-5A18D058C5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB803696-F603-4B0A-8F4A-EF2810757FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E794C9B1-78B5-4479-BF4F-91E9204B8E97}"/>
   </bookViews>
@@ -45,18 +45,12 @@
     <t>NIP</t>
   </si>
   <si>
-    <t>Kode</t>
-  </si>
-  <si>
     <t>Jenis Kelamin</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Jurusan</t>
-  </si>
-  <si>
     <t>Role</t>
   </si>
   <si>
@@ -75,7 +69,13 @@
     <t>P2MPP</t>
   </si>
   <si>
-    <t>Program Studi</t>
+    <t>Kode Dosen</t>
+  </si>
+  <si>
+    <t>Homebase Jurusan</t>
+  </si>
+  <si>
+    <t>Program Studi Mengajar</t>
   </si>
 </sst>
 </file>
@@ -491,7 +491,7 @@
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" style="4" customWidth="1"/>
     <col min="2" max="2" width="25.77734375" style="4" customWidth="1"/>
     <col min="3" max="3" width="40.77734375" style="6" customWidth="1"/>
     <col min="4" max="4" width="13.77734375" style="6" customWidth="1"/>
@@ -502,7 +502,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
@@ -511,13 +511,13 @@
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>12</v>
@@ -525,7 +525,7 @@
       <c r="H1" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="FL0AhQcqrH+fyjoFsXkB7bzU2XY2cRztrJqrYYVHHSxht33+l5L/3yYeMGkA7tRR1HQNQnIsXRqf8gCdUVCxAA==" saltValue="glUzJgzBOyIUCkcYZN2U/Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" insertRows="0" deleteRows="0"/>
+  <sheetProtection insertRows="0" deleteRows="0"/>
   <protectedRanges>
     <protectedRange sqref="A2:G1048576" name="Range1"/>
   </protectedRanges>
@@ -563,31 +563,31 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
